--- a/Test-Data.xlsx
+++ b/Test-Data.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cushwake1-my.sharepoint.com/personal/brian_mannlein_cushwake_com/Documents/1 - Apartment Team/Commission Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="8_{7F8678B9-85E4-4EC4-A774-C6888BEC35F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{474026F0-F8B4-4607-BD65-39DBA4D30CAB}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{7F8678B9-85E4-4EC4-A774-C6888BEC35F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{323D6602-8527-4712-A721-FEF02A59BE59}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7463A55-9E34-40E4-A2D4-1DEDA6E0A3B8}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="K158" s="6">
         <f t="shared" ca="1" si="15"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L158" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10132,7 +10132,7 @@
       </c>
       <c r="K159" s="6">
         <f t="shared" ca="1" si="15"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L159" s="8" t="str">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="K160" s="6">
         <f t="shared" ca="1" si="15"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L160" s="8" t="str">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="K161" s="6">
         <f t="shared" ca="1" si="15"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L161" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10290,8 +10290,8 @@
         <v>641922.31200000003</v>
       </c>
       <c r="K162" s="6">
-        <f t="shared" ref="K162:K193" ca="1" si="20">IF(B162&gt;DATE((YEAR(TODAY())-1),12,31), J162-(SUMIFS(H:H, B:B,"&gt;=" &amp; DATE(M162,1,1), B:B, "&lt;="&amp;TODAY())),"")</f>
-        <v>377535</v>
+        <f t="shared" ref="K162:K173" ca="1" si="20">IF(B162&gt;DATE((YEAR(TODAY())-1),12,31), J162-(SUMIFS(H:H, B:B,"&gt;=" &amp; DATE(M162,1,1), B:B, "&lt;="&amp;TODAY())),"")</f>
+        <v>238935</v>
       </c>
       <c r="L162" s="8" t="str">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10344,7 +10344,7 @@
       </c>
       <c r="K163" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L163" s="8" t="str">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="K164" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L164" s="8" t="str">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="K165" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L165" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="K166" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L166" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10522,7 +10522,7 @@
         <v>175</v>
       </c>
       <c r="B167" s="12">
-        <v>46296</v>
+        <v>46280</v>
       </c>
       <c r="C167" s="17">
         <v>7700000</v>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="I167" s="17">
         <f ca="1">IF(B167&lt;=TODAY(),Table1[[#This Row],[SPLIT]],0)</f>
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="J167" s="6">
         <f t="shared" si="19"/>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="K167" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L167" s="8" t="str">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="K168" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L168" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="K169" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L169" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="K170" s="6">
         <f t="shared" ca="1" si="20"/>
-        <v>377535</v>
+        <v>238935</v>
       </c>
       <c r="L170" s="8">
         <f>IF(Table1[[#This Row],[PRODUCT]]="APT",Table1[[#This Row],[SIZE]],"")</f>
